--- a/output/pdf_financials_xlsx/LI.xlsx
+++ b/output/pdf_financials_xlsx/LI.xlsx
@@ -7781,16 +7781,16 @@
         <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>17.01766</v>
+        <v>-0.823194</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>4.782672</v>
+        <v>4.633464</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>8.908706</v>
+        <v>8.203585</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>9.071666</v>
+        <v>8.980192000000001</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>-0.333757</v>
@@ -7799,16 +7799,16 @@
         <v>-0.264118</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-4.628029</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.201645</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-0.27882</v>
       </c>
     </row>
     <row r="119">
@@ -27738,7 +27738,11 @@
           <t>Exploration and evaluation assets expenditures 11</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -30354,7 +30358,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -34138,7 +34146,11 @@
           <t>Exploration and evaluation assets expenditures 10</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -37464,7 +37476,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -46868,7 +46884,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -52054,7 +52074,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LI.xlsx
+++ b/output/pdf_financials_xlsx/LI.xlsx
@@ -1083,22 +1083,22 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000175</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000117</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000108</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>7.6e-05</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000262</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.114906</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.889875</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2102,22 +2102,22 @@
         <v>-0.176576</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.085786</v>
+        <v>-0.085826</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.453231</v>
+        <v>-2.453406</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.097589</v>
+        <v>-0.097706</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.20974</v>
+        <v>-0.209848</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.03264</v>
+        <v>-0.032715</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.137938</v>
+        <v>-0.138014</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-5.024966</v>
@@ -2132,13 +2132,13 @@
         <v>-12.469132</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-12.961475</v>
+        <v>-12.961737</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-23.54676</v>
+        <v>-23.661666</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-35.666542</v>
+        <v>-36.556417</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-39.90409</v>
@@ -2228,22 +2228,22 @@
         <v>-0.176576</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.085786</v>
+        <v>-0.085826</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.453231</v>
+        <v>-2.453406</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.097589</v>
+        <v>-0.097706</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.20974</v>
+        <v>-0.209848</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.03264</v>
+        <v>-0.032715</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.137938</v>
+        <v>-0.138014</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-5.024966</v>
@@ -2258,13 +2258,13 @@
         <v>-12.469132</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-12.960344</v>
+        <v>-12.960606</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-23.512697</v>
+        <v>-23.627603</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-35.574476</v>
+        <v>-36.464351</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-39.60692</v>
@@ -2547,25 +2547,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.019925</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.01408</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000288</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002257</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001725</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.017887</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002573</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.153371</v>
@@ -2574,13 +2574,13 @@
         <v>0.856401</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.934384</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.040477</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.804628</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>5.506326</v>
@@ -2669,25 +2669,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.019925</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.01408</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000288</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002257</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001725</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.017887</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002573</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.153371</v>
@@ -2696,13 +2696,13 @@
         <v>0.856401</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.934384</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.040477</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.804628</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>5.506326</v>
@@ -3401,25 +3401,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.122391</v>
+        <v>0.102466</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.01408</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000288</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.002757</v>
+        <v>0.0005</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.013066</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.002573</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.00105</v>
@@ -3428,13 +3428,13 @@
         <v>0.101891</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.024818</v>
+        <v>0.090434</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.163595</v>
+        <v>0.123118</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.955515</v>
+        <v>0.150887</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.062405</v>
@@ -9674,7 +9674,11 @@
           <t>Reclamation deposits 8</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -11918,7 +11922,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -15490,7 +15498,11 @@
           <t>Reclamation deposits (Note 8)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -16556,7 +16568,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -16972,7 +16984,11 @@
           <t>Reclamation deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -17816,7 +17832,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -18542,7 +18562,11 @@
           <t>Reclamation deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -19164,7 +19188,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -19570,7 +19594,11 @@
           <t>RECLAMATION DEPOSITS (Note 4)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -21564,7 +21592,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -24938,7 +24966,11 @@
           <t>RECLAMATION DEPOSITS (Note 5)</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>0.014</v>
       </c>
@@ -27528,7 +27560,11 @@
           <t>Reclamation deposits 8</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -49312,7 +49348,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -51968,7 +52008,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -55128,7 +55172,11 @@
           <t>Proceeds from reclamation deposits</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -67594,7 +67642,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -73584,7 +73632,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -75378,7 +75426,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">

--- a/output/pdf_financials_xlsx/LI.xlsx
+++ b/output/pdf_financials_xlsx/LI.xlsx
@@ -570,10 +570,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -633,10 +631,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -696,10 +692,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -759,10 +753,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.126957</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.114367</v>
@@ -801,19 +793,19 @@
         <v>0.829731</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.602394</v>
+        <v>3.02621</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.91958</v>
+        <v>3.907164</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.97138</v>
+        <v>4.03838</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.54001</v>
+        <v>3.227012</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.837749</v>
+        <v>2.190745</v>
       </c>
     </row>
     <row r="8">
@@ -822,10 +814,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -885,10 +875,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.000167</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.000145</v>
@@ -948,10 +936,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.179178</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.151662</v>
@@ -1011,10 +997,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.179178</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.151662</v>
@@ -1074,10 +1058,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.013394</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1137,10 +1119,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -1200,10 +1180,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -1263,10 +1241,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -1326,10 +1302,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.179342</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.176576</v>
@@ -1389,10 +1363,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0.173086</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1646,10 +1618,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.006256</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.176576</v>
@@ -1709,10 +1679,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1772,10 +1740,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1896,10 +1862,8 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>-0.01</v>
@@ -1959,10 +1923,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>-0.01</v>
@@ -2093,10 +2055,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.192736</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.176576</v>
@@ -2156,10 +2116,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -2219,10 +2177,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.192736</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.176576</v>
@@ -2379,10 +2335,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-96.51169274347336</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -4465,25 +4419,25 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.092117</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.15827</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.670811</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.307053</v>
       </c>
       <c r="N64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>1.373242</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>1.556396</v>
       </c>
       <c r="Q64" s="3" t="n">
         <v>0</v>
@@ -4633,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.02875</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0153</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -4648,25 +4602,25 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.052313</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.068809</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.049037</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.069659</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.138787</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.095724</v>
       </c>
       <c r="Q67" s="3" t="n">
         <v>0</v>
@@ -6720,16 +6674,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000777</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.001623</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001122</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000452</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>-0.00511</v>
@@ -6741,7 +6695,7 @@
         <v>0.000751</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000114</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>-0.198021</v>
@@ -6753,7 +6707,7 @@
         <v>-0.088389</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.08109</v>
       </c>
       <c r="N101" s="3" t="n">
         <v>-0.002871</v>
@@ -7025,16 +6979,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.006749</v>
+        <v>0.005972</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.001809</v>
+        <v>-0.000186</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.008642</v>
+        <v>0.00752</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.02187</v>
+        <v>0.021418</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>-0.017097</v>
@@ -7046,7 +7000,7 @@
         <v>0.011803</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.013858</v>
+        <v>-0.013972</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>-0.065638</v>
@@ -7058,7 +7012,7 @@
         <v>0.277714</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.289437</v>
+        <v>-0.208347</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>0.102199</v>
@@ -7366,22 +7320,22 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.018662</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.041214</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017661</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.518566</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.080938</v>
       </c>
       <c r="S111" s="3" t="n">
-        <v>0</v>
+        <v>-0.260237</v>
       </c>
     </row>
     <row r="112">
@@ -7625,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>7.326023</v>
       </c>
     </row>
     <row r="116">
@@ -8811,22 +8765,22 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.018662</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.041214</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017661</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.518566</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.080938</v>
       </c>
       <c r="S134" s="3" t="n">
-        <v>0</v>
+        <v>-0.260237</v>
       </c>
     </row>
     <row r="135">
@@ -8878,22 +8832,22 @@
         <v>-2.800087</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-9.054192</v>
+        <v>-9.072854</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-13.429215</v>
+        <v>-13.470429</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-24.401606</v>
+        <v>-24.419267</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-23.227554</v>
+        <v>-23.74612</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-10.741971</v>
+        <v>-10.822909</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>-9.990755999999999</v>
+        <v>-10.250993</v>
       </c>
     </row>
   </sheetData>
@@ -8907,7 +8861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V664"/>
+  <dimension ref="A1:V677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27348,7 +27302,11 @@
           <t>Proceeds from sale of marketable securities 5</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -27670,7 +27628,11 @@
           <t>Purchase of equipment 9</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -30822,7 +30784,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -34604,7 +34570,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -37834,7 +37804,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -38364,7 +38338,11 @@
           <t>Proceeds from shares issuance</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -42814,7 +42792,11 @@
           <t>Proceeds from shares issuance</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -46816,7 +46798,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -49458,7 +49444,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -53608,7 +53598,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -55910,7 +55904,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -57716,7 +57714,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E465" s="5" t="n">
         <v>-0.173086</v>
       </c>
@@ -57926,7 +57928,11 @@
           <t>(Increase) decrease in GST receivable</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E467" s="5" t="n">
         <v>-0.000777</v>
       </c>
@@ -59934,7 +59940,11 @@
           <t>Management and directors fees 14</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E486" t="inlineStr">
         <is>
           <t>-</t>
@@ -62776,7 +62786,11 @@
           <t>Management and directors fees 12</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -65032,7 +65046,11 @@
           <t>Management and directors fees 12</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -66898,7 +66916,11 @@
           <t>Management and directors fees 13</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -73125,10 +73147,8 @@
         </is>
       </c>
       <c r="D612" t="inlineStr"/>
-      <c r="E612" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E612" s="5" t="n">
+        <v>0.052054</v>
       </c>
       <c r="F612" s="5" t="n">
         <v>0.03715</v>
@@ -77547,10 +77567,8 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E654" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E654" s="5" t="n">
+        <v>0.016175</v>
       </c>
       <c r="F654" s="5" t="n">
         <v>0.014271</v>
@@ -77655,10 +77673,8 @@
           <t>OtherOperatingExpenses</t>
         </is>
       </c>
-      <c r="E655" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E655" s="5" t="n">
+        <v>0.000167</v>
       </c>
       <c r="F655" s="5" t="n">
         <v>0.000145</v>
@@ -77763,10 +77779,8 @@
           <t>OperatingExpense</t>
         </is>
       </c>
-      <c r="E656" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E656" s="5" t="n">
+        <v>0.179178</v>
       </c>
       <c r="F656" s="5" t="n">
         <v>0.151662</v>
@@ -77871,10 +77885,8 @@
           <t>OperatingIncome</t>
         </is>
       </c>
-      <c r="E657" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E657" s="5" t="n">
+        <v>-0.179178</v>
       </c>
       <c r="F657" s="5" t="n">
         <v>-0.151662</v>
@@ -78613,10 +78625,8 @@
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E664" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E664" s="5" t="n">
+        <v>28.899156</v>
       </c>
       <c r="F664" s="5" t="n">
         <v>28.899156</v>
@@ -78695,6 +78705,1408 @@
         </is>
       </c>
       <c r="V664" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Management fees (Note 10) $</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E665" s="5" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F665" s="5" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Office and general (Note 10)</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E666" s="5" t="n">
+        <v>0.012782</v>
+      </c>
+      <c r="F666" s="5" t="n">
+        <v>0.004096</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E667" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Administration fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E668" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>OTHER (EXPENSES) INCOME</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E669" s="5" t="n">
+        <v>0.013394</v>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>OTHER (EXPENSES) INCOME</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E670" s="5" t="n">
+        <v>-0.013558</v>
+      </c>
+      <c r="F670" s="5" t="n">
+        <v>-0.000693</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>OTHER (EXPENSES) INCOME</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Write-off of mineral property</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr"/>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F671" s="5" t="n">
+        <v>-0.024221</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>OTHER (EXPENSES) INCOME</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAX</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E672" s="5" t="n">
+        <v>-0.179342</v>
+      </c>
+      <c r="F672" s="5" t="n">
+        <v>-0.176576</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>INCOME TAXES</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Future income tax recovery</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E673" s="5" t="n">
+        <v>0.173086</v>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>INCOME TAXES</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E674" s="5" t="n">
+        <v>-0.006256</v>
+      </c>
+      <c r="F674" s="5" t="n">
+        <v>-0.176576</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>INCOME TAXES</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>DEFICIT, BEGINNING OF YEAR</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" s="5" t="n">
+        <v>-2.469714</v>
+      </c>
+      <c r="F675" s="5" t="n">
+        <v>-2.47597</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>INCOME TAXES</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>DEFICIT, END OF YEAR $ $</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" s="5" t="n">
+        <v>-2.47597</v>
+      </c>
+      <c r="F676" s="5" t="n">
+        <v>-2.652546</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>INCOME TAXES</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Loss per Share – Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E677" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F677" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V677" t="inlineStr">
         <is>
           <t>-</t>
         </is>
